--- a/data/trans_dic/Q45B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 5,94</t>
+          <t>1,97; 5,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,24</t>
+          <t>2,02; 6,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,18</t>
+          <t>0,23; 2,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 17,91</t>
+          <t>9,72; 17,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 19,06</t>
+          <t>10,42; 19,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 7,19</t>
+          <t>2,27; 6,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 9,8</t>
+          <t>5,57; 9,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,4</t>
+          <t>6,04; 10,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,78</t>
+          <t>1,49; 3,71</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,43</t>
+          <t>0,24; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,57</t>
+          <t>1,25; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,89; 22,81</t>
+          <t>14,6; 22,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 19,15</t>
+          <t>10,69; 18,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,78</t>
+          <t>2,63; 6,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,01; 12,43</t>
+          <t>7,91; 12,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 9,94</t>
+          <t>6,02; 10,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 3,67</t>
+          <t>1,43; 3,58</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,83</t>
+          <t>1,2; 3,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,41</t>
+          <t>1,65; 4,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,96</t>
+          <t>0,2; 1,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,26; 16,8</t>
+          <t>6,86; 16,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 15,08</t>
+          <t>7,07; 14,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 10,03</t>
+          <t>3,33; 10,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,97</t>
+          <t>3,07; 5,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,75</t>
+          <t>3,74; 7,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,45</t>
+          <t>1,17; 3,33</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,48</t>
+          <t>1,1; 2,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,77</t>
+          <t>1,74; 3,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,83</t>
+          <t>0,5; 1,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,29</t>
+          <t>6,46; 10,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,54</t>
+          <t>6,43; 10,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,68</t>
+          <t>4,38; 7,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,07</t>
+          <t>3,28; 5,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,91; 5,96</t>
+          <t>4,04; 5,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 3,92</t>
+          <t>2,33; 3,84</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,26</t>
+          <t>1,0; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,44</t>
+          <t>0,41; 2,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,54</t>
+          <t>0,62; 2,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,81</t>
+          <t>3,13; 6,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,15</t>
+          <t>2,48; 5,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,66</t>
+          <t>1,27; 3,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,2</t>
+          <t>2,53; 5,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,61</t>
+          <t>1,82; 3,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 2,67</t>
+          <t>1,2; 2,76</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,08</t>
+          <t>0,34; 3,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,76</t>
+          <t>0,85; 4,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,83</t>
+          <t>0,34; 2,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,22</t>
+          <t>2,92; 5,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,4; 6,01</t>
+          <t>3,42; 5,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,72</t>
+          <t>1,17; 2,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,42</t>
+          <t>2,58; 4,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,53</t>
+          <t>3,13; 5,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,43</t>
+          <t>1,03; 2,42</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,6</t>
+          <t>1,58; 2,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,1</t>
+          <t>2,04; 3,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,31</t>
+          <t>0,67; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 8,74</t>
+          <t>6,85; 8,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,29</t>
+          <t>6,48; 8,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,17</t>
+          <t>2,98; 4,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,51</t>
+          <t>4,42; 5,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,47; 5,53</t>
+          <t>4,48; 5,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,65</t>
+          <t>1,96; 2,67</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas</t>
+          <t>Población que han utilizado en los últimos 5 años cabinas o lámparas de rayos ultravioletas (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9486; 28142</t>
+          <t>9341; 27819</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8622; 27193</t>
+          <t>8803; 27099</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1020; 9357</t>
+          <t>1007; 9385</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30075; 54939</t>
+          <t>29816; 54874</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33328; 59777</t>
+          <t>32678; 60308</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8969; 24951</t>
+          <t>7882; 23596</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45927; 76490</t>
+          <t>43459; 76514</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45115; 77929</t>
+          <t>45272; 79257</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11663; 29344</t>
+          <t>11577; 28822</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>892; 8921</t>
+          <t>878; 8043</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5228; 19076</t>
+          <t>5220; 19004</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6822</t>
+          <t>0; 6791</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>55366; 84836</t>
+          <t>54308; 85269</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36587; 64496</t>
+          <t>36000; 62733</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9686; 25178</t>
+          <t>9753; 24871</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59162; 91829</t>
+          <t>58436; 90374</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>43920; 75005</t>
+          <t>45407; 76898</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10830; 27221</t>
+          <t>10605; 26508</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6627; 20781</t>
+          <t>6503; 20091</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11023; 27564</t>
+          <t>10319; 27061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1103; 10189</t>
+          <t>1027; 10029</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12188; 28189</t>
+          <t>11503; 27639</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18561; 39238</t>
+          <t>18387; 38984</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5469; 16583</t>
+          <t>5504; 17460</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21726; 42429</t>
+          <t>21795; 42484</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31687; 59778</t>
+          <t>33085; 62075</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8524; 23672</t>
+          <t>8032; 22872</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13102; 30772</t>
+          <t>13579; 33928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19275; 43381</t>
+          <t>20023; 42717</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6067; 21030</t>
+          <t>5733; 19161</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>45371; 73481</t>
+          <t>46116; 76282</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48973; 80622</t>
+          <t>49168; 79486</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35682; 63055</t>
+          <t>35981; 62210</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>63509; 99092</t>
+          <t>64037; 97683</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>75030; 114295</t>
+          <t>77425; 114370</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46767; 77094</t>
+          <t>45839; 75581</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3024; 14947</t>
+          <t>3523; 14954</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2059; 12442</t>
+          <t>2071; 12938</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3934; 15742</t>
+          <t>3846; 15144</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17373; 38710</t>
+          <t>17792; 38882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18761; 39024</t>
+          <t>18745; 39613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9905; 26849</t>
+          <t>9311; 26153</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23788; 47803</t>
+          <t>23298; 46734</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22548; 45798</t>
+          <t>23063; 47372</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16819; 36138</t>
+          <t>16306; 37338</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>998; 9186</t>
+          <t>1021; 9797</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2294; 12692</t>
+          <t>2276; 12527</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>959; 8034</t>
+          <t>954; 8160</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>37464; 65134</t>
+          <t>36411; 63116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37591; 66333</t>
+          <t>37804; 65192</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11977; 29322</t>
+          <t>12685; 28866</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39756; 68353</t>
+          <t>39903; 67868</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>44019; 75784</t>
+          <t>42965; 74749</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13845; 33168</t>
+          <t>14051; 32941</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51398; 85126</t>
+          <t>51538; 85211</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>68840; 105742</t>
+          <t>69476; 106489</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21959; 44238</t>
+          <t>22582; 44589</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>234426; 295277</t>
+          <t>231369; 293207</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>231923; 293016</t>
+          <t>229233; 298144</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>105326; 146727</t>
+          <t>105034; 150065</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>293629; 366104</t>
+          <t>293685; 369798</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>310293; 383771</t>
+          <t>311226; 385503</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>133535; 182358</t>
+          <t>134945; 184009</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q45B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Q45B_R-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,87</t>
+          <t>2,05; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,21</t>
+          <t>2,12; 6,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,19</t>
+          <t>0,24; 2,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,72; 17,89</t>
+          <t>9,63; 17,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 19,23</t>
+          <t>10,15; 19,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,8</t>
+          <t>2,31; 7,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,8</t>
+          <t>5,68; 9,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,57</t>
+          <t>6,04; 10,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,71</t>
+          <t>1,51; 3,68</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,19</t>
+          <t>0,24; 2,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,55</t>
+          <t>1,21; 4,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,6; 22,93</t>
+          <t>15,01; 23,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,69; 18,62</t>
+          <t>10,92; 18,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,7</t>
+          <t>2,4; 6,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,23</t>
+          <t>7,65; 11,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 10,19</t>
+          <t>5,96; 9,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,58</t>
+          <t>1,5; 3,68</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,7</t>
+          <t>1,21; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,33</t>
+          <t>1,75; 4,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,93</t>
+          <t>0,2; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,86; 16,47</t>
+          <t>6,95; 17,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,07; 14,99</t>
+          <t>7,19; 14,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 10,56</t>
+          <t>3,35; 10,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,98</t>
+          <t>2,99; 6,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,01</t>
+          <t>3,64; 6,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,33</t>
+          <t>1,15; 3,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,74</t>
+          <t>1,05; 2,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,71</t>
+          <t>1,61; 3,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,67</t>
+          <t>0,52; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 10,68</t>
+          <t>6,42; 10,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,39</t>
+          <t>6,57; 10,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,57</t>
+          <t>4,44; 7,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,0</t>
+          <t>3,26; 5,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,97</t>
+          <t>3,89; 5,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,84</t>
+          <t>2,35; 3,94</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,27</t>
+          <t>0,91; 4,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,53</t>
+          <t>0,47; 2,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,44</t>
+          <t>0,61; 2,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,13; 6,84</t>
+          <t>3,17; 6,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,23</t>
+          <t>2,39; 5,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,56</t>
+          <t>1,34; 3,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,08</t>
+          <t>2,45; 5,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,74</t>
+          <t>1,85; 3,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,76</t>
+          <t>1,19; 2,66</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,29</t>
+          <t>0,34; 3,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,69</t>
+          <t>0,77; 4,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,87</t>
+          <t>0,34; 2,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,05</t>
+          <t>3,01; 5,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,42; 5,9</t>
+          <t>3,47; 5,96</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,67</t>
+          <t>1,05; 2,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,39</t>
+          <t>2,64; 4,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,45</t>
+          <t>3,14; 5,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,42</t>
+          <t>1,07; 2,46</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 2,61</t>
+          <t>1,52; 2,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,12</t>
+          <t>1,99; 3,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,32</t>
+          <t>0,65; 1,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,85; 8,68</t>
+          <t>7,0; 8,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,43</t>
+          <t>6,55; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,26</t>
+          <t>3,04; 4,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 5,56</t>
+          <t>4,47; 5,49</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,55</t>
+          <t>4,48; 5,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,67</t>
+          <t>1,93; 2,64</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9341; 27819</t>
+          <t>9724; 26975</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8803; 27099</t>
+          <t>9263; 26382</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1007; 9385</t>
+          <t>1011; 9069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29816; 54874</t>
+          <t>29545; 53199</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32678; 60308</t>
+          <t>31815; 60228</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7882; 23596</t>
+          <t>8034; 24673</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43459; 76514</t>
+          <t>44340; 74941</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45272; 79257</t>
+          <t>45301; 78914</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11577; 28822</t>
+          <t>11715; 28541</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>878; 8043</t>
+          <t>883; 9037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5220; 19004</t>
+          <t>5049; 16952</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6791</t>
+          <t>0; 6839</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>54308; 85269</t>
+          <t>55826; 86635</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36000; 62733</t>
+          <t>36783; 63514</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9753; 24871</t>
+          <t>8906; 23755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58436; 90374</t>
+          <t>56545; 88186</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45407; 76898</t>
+          <t>44967; 75086</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10605; 26508</t>
+          <t>11083; 27302</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6503; 20091</t>
+          <t>6565; 21757</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10319; 27061</t>
+          <t>10922; 27721</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1027; 10029</t>
+          <t>1031; 10350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11503; 27639</t>
+          <t>11662; 28712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18387; 38984</t>
+          <t>18708; 38701</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5504; 17460</t>
+          <t>5535; 17679</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21795; 42484</t>
+          <t>21246; 44038</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33085; 62075</t>
+          <t>32198; 59824</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8032; 22872</t>
+          <t>7903; 23260</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13579; 33928</t>
+          <t>13027; 32213</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20023; 42717</t>
+          <t>18530; 42151</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5733; 19161</t>
+          <t>5933; 19251</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46116; 76282</t>
+          <t>45885; 75897</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>49168; 79486</t>
+          <t>50248; 79259</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35981; 62210</t>
+          <t>36467; 64186</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64037; 97683</t>
+          <t>63613; 99085</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>77425; 114370</t>
+          <t>74544; 112634</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45839; 75581</t>
+          <t>46326; 77531</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3523; 14954</t>
+          <t>3175; 15453</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2071; 12938</t>
+          <t>2391; 14436</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3846; 15144</t>
+          <t>3800; 15437</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17792; 38882</t>
+          <t>18031; 39629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>18745; 39613</t>
+          <t>18113; 38970</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9311; 26153</t>
+          <t>9842; 27350</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23298; 46734</t>
+          <t>22560; 47203</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23063; 47372</t>
+          <t>23490; 46559</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16306; 37338</t>
+          <t>16088; 35978</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1021; 9797</t>
+          <t>1001; 9615</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2276; 12527</t>
+          <t>2056; 12624</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>954; 8160</t>
+          <t>954; 8329</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36411; 63116</t>
+          <t>37560; 63957</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37804; 65192</t>
+          <t>38329; 65844</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12685; 28866</t>
+          <t>11388; 28286</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39903; 67868</t>
+          <t>40873; 69092</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>42965; 74749</t>
+          <t>43062; 72880</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14051; 32941</t>
+          <t>14569; 33515</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>51538; 85211</t>
+          <t>49561; 84639</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>69476; 106489</t>
+          <t>67997; 105486</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22582; 44589</t>
+          <t>21747; 43976</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>231369; 293207</t>
+          <t>236515; 298662</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>229233; 298144</t>
+          <t>231644; 294144</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>105034; 150065</t>
+          <t>106871; 147850</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>293685; 369798</t>
+          <t>297184; 365039</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>311226; 385503</t>
+          <t>311038; 384560</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>134945; 184009</t>
+          <t>133006; 182180</t>
         </is>
       </c>
     </row>
